--- a/Unsorted/Петергоф/до войны/петергоф_до войны_подписи.xlsx
+++ b/Unsorted/Петергоф/до войны/петергоф_до войны_подписи.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,6 @@
     <sheet name="Sheet6" sheetId="6" r:id="rId4"/>
     <sheet name="Sheet8" sheetId="8" r:id="rId5"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
   <si>
     <t>подпись</t>
   </si>
@@ -121,9 +120,6 @@
   </si>
   <si>
     <t>подзаголовок</t>
-  </si>
-  <si>
-    <t>Петергоф. Вид на фонтаны Нижнего парка. Май 1937</t>
   </si>
   <si>
     <t xml:space="preserve">Петергоф. Вид на дворец. 1936 г. 
@@ -768,7 +764,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -812,7 +808,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
@@ -820,7 +816,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="57.6">
@@ -828,7 +824,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +870,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="72">
@@ -882,7 +878,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -891,7 +887,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="12"/>
     </row>
@@ -900,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -909,7 +905,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -918,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -927,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="12"/>
     </row>
@@ -936,7 +932,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="57.6">
@@ -944,7 +940,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -993,7 +989,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1036,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1087,7 +1083,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -1096,70 +1092,70 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:3" ht="57.6">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:3" ht="57.6">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" ht="72">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:3" ht="57.6">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" spans="1:3" ht="72">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" spans="1:3" ht="43.2">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" spans="1:3" ht="57.6">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -1176,7 +1172,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.47265625" customWidth="1"/>
@@ -1209,7 +1205,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -1218,7 +1214,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -1227,7 +1223,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" s="12"/>
     </row>
@@ -1236,127 +1232,86 @@
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" ht="72">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:3" ht="43.2">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" spans="1:3" ht="57.6">
       <c r="A10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" spans="1:3" ht="57.6">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" spans="1:3" ht="43.2">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" spans="1:3" ht="57.6">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" s="12"/>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor theme="7" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="24.47265625" customWidth="1"/>
-    <col min="2" max="2" width="58.7890625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.6">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="57.6">
-      <c r="A4" s="2" t="s">
+    <row r="14" spans="1:3" ht="57.6">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="57.6">
-      <c r="A5" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="57.6">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="57.6">
-      <c r="A6" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="57.6">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>79</v>
+      <c r="B16" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
